--- a/data/trans_orig/P1429-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2007</t>
+          <t>Población con diagnóstico de osteoporosis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>23184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461968</t>
+          <t>462231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472765</t>
+          <t>472306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289039</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>300901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756124</t>
+          <t>757273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772034</t>
+          <t>772593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359504</t>
+          <t>359483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366129</t>
+          <t>366127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355933</t>
+          <t>356115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368515</t>
+          <t>368640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721123</t>
+          <t>719932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733424</t>
+          <t>733399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529879</t>
+          <t>529380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153476</t>
+          <t>153025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164502</t>
+          <t>164451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687833</t>
+          <t>688203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703059</t>
+          <t>703196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26754</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35320</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55854</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1211580</t>
+          <t>1210682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1227297</t>
+          <t>1227792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678965</t>
+          <t>678134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698344</t>
+          <t>697648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1896766</t>
+          <t>1898075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922905</t>
+          <t>1922169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37065</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339887</t>
+          <t>340418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349515</t>
+          <t>349502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537725</t>
+          <t>536711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555541</t>
+          <t>555840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>882242</t>
+          <t>883425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902810</t>
+          <t>903113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>58887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>58516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92779</t>
+          <t>92270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1155929</t>
+          <t>1156472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1188775</t>
+          <t>1189873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1454181</t>
+          <t>1454690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1488200</t>
+          <t>1488444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47957</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124960</t>
+          <t>124433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173438</t>
+          <t>169290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>154553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205580</t>
+          <t>206959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3222233</t>
+          <t>3224240</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3246425</t>
+          <t>3246995</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3204686</t>
+          <t>3208834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3253164</t>
+          <t>3253691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6442734</t>
+          <t>6441355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6492857</t>
+          <t>6493761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2012</t>
+          <t>Población con diagnóstico de osteoporosis en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429462</t>
+          <t>430338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301324</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312503</t>
+          <t>312498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736333</t>
+          <t>735832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747784</t>
+          <t>747770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328374</t>
+          <t>327764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336939</t>
+          <t>336961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>747451</t>
+          <t>745665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755821</t>
+          <t>754896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618259</t>
+          <t>616127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246014</t>
+          <t>247236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257465</t>
+          <t>257455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871632</t>
+          <t>870932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>885921</t>
+          <t>886262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1152008</t>
+          <t>1152062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743887</t>
+          <t>743602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758419</t>
+          <t>757575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900765</t>
+          <t>1900871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915778</t>
+          <t>1915523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56265</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>58145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>505194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703981</t>
+          <t>705160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729424</t>
+          <t>728730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1213936</t>
+          <t>1212698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238776</t>
+          <t>1239908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54393</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89444</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54856</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91130</t>
+          <t>88801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1018799</t>
+          <t>1017075</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1053850</t>
+          <t>1053036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1283995</t>
+          <t>1286324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320269</t>
+          <t>1320841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121034</t>
+          <t>119391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169369</t>
+          <t>167586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126502</t>
+          <t>123385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177692</t>
+          <t>173768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3405040</t>
+          <t>3405663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3418871</t>
+          <t>3418840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3376437</t>
+          <t>3378220</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3424772</t>
+          <t>3426415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6789021</t>
+          <t>6792945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6840211</t>
+          <t>6843328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2016</t>
+          <t>Población con diagnóstico de osteoporosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421634</t>
+          <t>422358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331733</t>
+          <t>331915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343780</t>
+          <t>343879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759173</t>
+          <t>757185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772032</t>
+          <t>771541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>358825</t>
+          <t>359937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371023</t>
+          <t>371031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735989</t>
+          <t>736769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748256</t>
+          <t>747687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512075</t>
+          <t>512786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520914</t>
+          <t>520922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148266</t>
+          <t>147789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162402</t>
+          <t>162364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665975</t>
+          <t>665290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682280</t>
+          <t>681590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1142553</t>
+          <t>1142705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>798195</t>
+          <t>798090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>815623</t>
+          <t>815571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945725</t>
+          <t>1945080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963128</t>
+          <t>1964087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610328</t>
+          <t>611035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618998</t>
+          <t>619014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707425</t>
+          <t>705587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726358</t>
+          <t>725271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1321136</t>
+          <t>1322974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1342843</t>
+          <t>1342616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47500</t>
+          <t>45641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46173</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79356</t>
+          <t>79042</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1002865</t>
+          <t>1003871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1034525</t>
+          <t>1036384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1289814</t>
+          <t>1290128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1322997</t>
+          <t>1323106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98931</t>
+          <t>99667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143895</t>
+          <t>146172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111740</t>
+          <t>109252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161526</t>
+          <t>159063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3364352</t>
+          <t>3366386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379316</t>
+          <t>3379437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3387701</t>
+          <t>3385424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3432665</t>
+          <t>3431929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6755792</t>
+          <t>6758255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6805578</t>
+          <t>6808066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2023</t>
+          <t>Población con diagnóstico de osteoporosis en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495362</t>
+          <t>495300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502378</t>
+          <t>502291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427494</t>
+          <t>427161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>437641</t>
+          <t>437989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926710</t>
+          <t>925693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>938572</t>
+          <t>938389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448848</t>
+          <t>448817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363628</t>
+          <t>363146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373804</t>
+          <t>373838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>814195</t>
+          <t>813653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824806</t>
+          <t>824848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655307</t>
+          <t>655240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666920</t>
+          <t>666364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143562</t>
+          <t>144310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158471</t>
+          <t>158458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>802238</t>
+          <t>803963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827556</t>
+          <t>827642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35371</t>
+          <t>35977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55750</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004269</t>
+          <t>1003903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025313</t>
+          <t>1024830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>938984</t>
+          <t>938378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961353</t>
+          <t>963719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952677</t>
+          <t>1949998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980083</t>
+          <t>1980446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31797</t>
+          <t>33530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56554</t>
+          <t>58222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59418</t>
+          <t>59597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466911</t>
+          <t>467182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472101</t>
+          <t>472120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>779250</t>
+          <t>777582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>804007</t>
+          <t>802274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1249114</t>
+          <t>1248935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1271014</t>
+          <t>1270266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57294</t>
+          <t>58467</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37798</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58390</t>
+          <t>58571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237935</t>
+          <t>237077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>701651</t>
+          <t>700478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720767</t>
+          <t>719914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941062</t>
+          <t>940881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>961654</t>
+          <t>960606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>128417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179345</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157529</t>
+          <t>154301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209876</t>
+          <t>210175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3327187</t>
+          <t>3325294</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352414</t>
+          <t>3352116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3384139</t>
+          <t>3381493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3434789</t>
+          <t>3435067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6723690</t>
+          <t>6723391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6776037</t>
+          <t>6779265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1429-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462231</t>
+          <t>462484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472306</t>
+          <t>472704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287035</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300901</t>
+          <t>301148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757273</t>
+          <t>756496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772593</t>
+          <t>772139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359483</t>
+          <t>359559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366127</t>
+          <t>366124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356115</t>
+          <t>356984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368640</t>
+          <t>368971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719932</t>
+          <t>721114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733399</t>
+          <t>733875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529380</t>
+          <t>528507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540508</t>
+          <t>540534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153025</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164451</t>
+          <t>164680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>688203</t>
+          <t>687519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703196</t>
+          <t>703168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1210682</t>
+          <t>1211309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1227792</t>
+          <t>1228038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678134</t>
+          <t>678742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697648</t>
+          <t>697924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898075</t>
+          <t>1896656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922169</t>
+          <t>1921236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340418</t>
+          <t>340269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349502</t>
+          <t>349459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>536711</t>
+          <t>536612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555840</t>
+          <t>555444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>883425</t>
+          <t>883766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>903113</t>
+          <t>903553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58887</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92288</t>
+          <t>92921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58516</t>
+          <t>56931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1156472</t>
+          <t>1155839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1189873</t>
+          <t>1191985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1454690</t>
+          <t>1455023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1488444</t>
+          <t>1490029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124433</t>
+          <t>122654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169290</t>
+          <t>168304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154553</t>
+          <t>153227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206959</t>
+          <t>207309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3224240</t>
+          <t>3223566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3246995</t>
+          <t>3246394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3208834</t>
+          <t>3209820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3253691</t>
+          <t>3255470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6441355</t>
+          <t>6441005</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6493761</t>
+          <t>6495087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430338</t>
+          <t>431387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301140</t>
+          <t>301926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312498</t>
+          <t>312539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735832</t>
+          <t>735223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747770</t>
+          <t>747840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327764</t>
+          <t>327983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336961</t>
+          <t>337008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>745665</t>
+          <t>747490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754896</t>
+          <t>755824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616127</t>
+          <t>619830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247236</t>
+          <t>246075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257455</t>
+          <t>257484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>886262</t>
+          <t>885562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1152062</t>
+          <t>1152043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743602</t>
+          <t>743935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757575</t>
+          <t>758430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900871</t>
+          <t>1900276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915523</t>
+          <t>1915527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>56493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58145</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505194</t>
+          <t>505253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705160</t>
+          <t>703753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728730</t>
+          <t>729826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212698</t>
+          <t>1213539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1239908</t>
+          <t>1239529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91168</t>
+          <t>89112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>56544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88801</t>
+          <t>90715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1017075</t>
+          <t>1019131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1053036</t>
+          <t>1052849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1286324</t>
+          <t>1284410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320841</t>
+          <t>1318581</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119391</t>
+          <t>119863</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167586</t>
+          <t>168158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123385</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173768</t>
+          <t>175936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3405663</t>
+          <t>3406674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3418840</t>
+          <t>3418845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3378220</t>
+          <t>3377648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3426415</t>
+          <t>3425943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6792945</t>
+          <t>6790777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6843328</t>
+          <t>6841449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422358</t>
+          <t>422475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331915</t>
+          <t>332569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343879</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757185</t>
+          <t>758138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771541</t>
+          <t>771077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359937</t>
+          <t>359203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371031</t>
+          <t>371011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736769</t>
+          <t>737244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747687</t>
+          <t>748256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512786</t>
+          <t>512626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520922</t>
+          <t>520908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147789</t>
+          <t>147462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162364</t>
+          <t>162435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665290</t>
+          <t>665319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681590</t>
+          <t>681429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30434</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1142705</t>
+          <t>1142272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>798090</t>
+          <t>799457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>815571</t>
+          <t>815955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945080</t>
+          <t>1945830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964087</t>
+          <t>1963967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611035</t>
+          <t>611076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619014</t>
+          <t>618981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705587</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>725271</t>
+          <t>725310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1322974</t>
+          <t>1321191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1342616</t>
+          <t>1342799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45641</t>
+          <t>46550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78154</t>
+          <t>78984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79042</t>
+          <t>78343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1003871</t>
+          <t>1003041</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036384</t>
+          <t>1035475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1290128</t>
+          <t>1290827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1323106</t>
+          <t>1323176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99667</t>
+          <t>100870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146172</t>
+          <t>145879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109252</t>
+          <t>109823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159063</t>
+          <t>159221</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3366386</t>
+          <t>3365365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379437</t>
+          <t>3379554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3385424</t>
+          <t>3385717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3431929</t>
+          <t>3430726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6758255</t>
+          <t>6758097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6808066</t>
+          <t>6807495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500087</t>
+          <t>545105</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495300</t>
+          <t>539660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502291</t>
+          <t>547468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>433167</t>
+          <t>473152</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427161</t>
+          <t>467323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>437989</t>
+          <t>478259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>933254</t>
+          <t>1018257</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925693</t>
+          <t>1011103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>938389</t>
+          <t>1024320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503536</t>
+          <t>548877</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503536</t>
+          <t>548877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503536</t>
+          <t>548877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446186</t>
+          <t>486997</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446186</t>
+          <t>486997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446186</t>
+          <t>486997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949722</t>
+          <t>1035874</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949722</t>
+          <t>1035874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949722</t>
+          <t>1035874</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>451125</t>
+          <t>482050</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448817</t>
+          <t>479959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451696</t>
+          <t>482714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>369317</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363146</t>
+          <t>402076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373838</t>
+          <t>412869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>820442</t>
+          <t>890430</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813653</t>
+          <t>883808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824848</t>
+          <t>895260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451696</t>
+          <t>482714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451696</t>
+          <t>482714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451696</t>
+          <t>482714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421775</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421775</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832978</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832978</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832978</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>662583</t>
+          <t>465795</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655240</t>
+          <t>460492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666364</t>
+          <t>468879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>153355</t>
+          <t>172498</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144310</t>
+          <t>162300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158458</t>
+          <t>178420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>815938</t>
+          <t>638293</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>803963</t>
+          <t>625489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827642</t>
+          <t>645127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>36208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41180</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58429</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1018237</t>
+          <t>1114767</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1003903</t>
+          <t>1099198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1024830</t>
+          <t>1121687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>949010</t>
+          <t>828647</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>938378</t>
+          <t>820136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>963719</t>
+          <t>835059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1967247</t>
+          <t>1943413</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949998</t>
+          <t>1928552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980446</t>
+          <t>1953594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034072</t>
+          <t>1130969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034072</t>
+          <t>1130969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034072</t>
+          <t>1130969</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>974355</t>
+          <t>856344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>974355</t>
+          <t>856344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>974355</t>
+          <t>856344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2008427</t>
+          <t>1987312</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2008427</t>
+          <t>1987312</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2008427</t>
+          <t>1987312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33530</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>61383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>44091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59597</t>
+          <t>65907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>470400</t>
+          <t>562957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467182</t>
+          <t>559283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472120</t>
+          <t>564873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>789949</t>
+          <t>775491</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>777582</t>
+          <t>765386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>802274</t>
+          <t>785307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1260350</t>
+          <t>1338448</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1248935</t>
+          <t>1326440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1270266</t>
+          <t>1348256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>835804</t>
+          <t>826769</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>835804</t>
+          <t>826769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>835804</t>
+          <t>826769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1308532</t>
+          <t>1392347</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1308532</t>
+          <t>1392347</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1308532</t>
+          <t>1392347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39031</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>47767</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>64351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240017</t>
+          <t>236710</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>234135</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>711668</t>
+          <t>790238</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>700478</t>
+          <t>778975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>719914</t>
+          <t>800559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>951685</t>
+          <t>1026948</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940881</t>
+          <t>1014516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>960606</t>
+          <t>1037183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>758945</t>
+          <t>841639</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>758945</t>
+          <t>841639</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>758945</t>
+          <t>841639</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999452</t>
+          <t>1078867</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999452</t>
+          <t>1078867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999452</t>
+          <t>1078867</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>157018</t>
+          <t>172617</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128417</t>
+          <t>153431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181991</t>
+          <t>193613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>184651</t>
+          <t>201342</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154301</t>
+          <t>177467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210175</t>
+          <t>223610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3342450</t>
+          <t>3407384</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3325294</t>
+          <t>3393896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352116</t>
+          <t>3416270</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3406466</t>
+          <t>3448405</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3381493</t>
+          <t>3427409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3435067</t>
+          <t>3467591</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6748915</t>
+          <t>6855788</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6723391</t>
+          <t>6833520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6779265</t>
+          <t>6879663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370083</t>
+          <t>3436109</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370083</t>
+          <t>3436109</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370083</t>
+          <t>3436109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3563484</t>
+          <t>3621022</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3563484</t>
+          <t>3621022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3563484</t>
+          <t>3621022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6933566</t>
+          <t>7057130</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6933566</t>
+          <t>7057130</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6933566</t>
+          <t>7057130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
